--- a/data/trans_camb/P1805_2016_2023-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1805_2016_2023-Provincia-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-2,47</t>
+          <t>-2,67</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-4,6</t>
+          <t>-4,67</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,55</t>
+          <t>-3,66</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,08</t>
+          <t>-5,45; -0,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; -1,44</t>
+          <t>-8,64; -1,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,99; -1,7</t>
+          <t>-5,89; -1,74</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-67,6%</t>
+          <t>-73,03%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-63,28%</t>
+          <t>-64,27%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-65,12%</t>
+          <t>-67,17%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-93,93; 41,41</t>
+          <t>-100,0; 7,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,78; -26,04</t>
+          <t>-82,68; -28,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-82,85; -36,84</t>
+          <t>-82,23; -37,64</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,55</t>
+          <t>3,34</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>2,74</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,22</t>
+          <t>3,03</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,06</t>
+          <t>1,68; 6,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,15</t>
+          <t>1,22; 5,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,06</t>
+          <t>1,75; 4,67</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>876,85%</t>
+          <t>825,22%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>250,8%</t>
+          <t>235,21%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>407,33%</t>
+          <t>382,86%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,4; —</t>
+          <t>90,29; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,53; 789,93</t>
+          <t>40,86; 834,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140,3; 1173,76</t>
+          <t>120,74; 1044,14</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,92</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>1,33</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,98</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,88</t>
+          <t>-0,67; 4,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 3,94</t>
+          <t>-2,11; 3,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,07</t>
+          <t>-0,8; 3,32</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>103,91%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,03; 652,73</t>
+          <t>-38,4; 848,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,98; 139,22</t>
+          <t>-34,69; 157,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,32; 144,47</t>
+          <t>-19,17; 163,19</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4,05</t>
+          <t>3,27</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>2,58</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>2,92</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 8,28</t>
+          <t>0,33; 7,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 4,21</t>
+          <t>-0,33; 5,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 4,81</t>
+          <t>0,84; 5,37</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>162,37%</t>
+          <t>131,1%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>101,45%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,16; 569,23</t>
+          <t>-1,74; 572,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 201,95</t>
+          <t>-9,78; 267,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,91; 222,26</t>
+          <t>16,7; 268,39</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-2,27</t>
+          <t>-2,31</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-1,24</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,53; -0,13</t>
+          <t>-5,58; -0,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,48</t>
+          <t>-2,76; 1,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,19</t>
+          <t>-3,15; 0,22</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-74,84%</t>
+          <t>-76,21%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-9,2%</t>
+          <t>-13,29%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-49,68%</t>
+          <t>-52,53%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 30,99</t>
+          <t>-100,0; 113,97</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-73,69; 309,5</t>
+          <t>-82,9; 259,63</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,65; 25,65</t>
+          <t>-81,07; 43,05</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-0,51</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,47</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 3,55</t>
+          <t>-0,73; 3,58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 2,09</t>
+          <t>-3,42; 2,24</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,13</t>
+          <t>-1,37; 2,21</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>131,62%</t>
+          <t>120,95%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-13,24%</t>
+          <t>-9,46%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-42,92; 1086,45</t>
+          <t>-53,63; 1064,65</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-60,65; 96,71</t>
+          <t>-61,73; 105,72</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-37,46; 145,89</t>
+          <t>-39,36; 147,43</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>3,05</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>3,4</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,88</t>
+          <t>1,8; 6,38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 4,65</t>
+          <t>0,6; 5,56</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,9</t>
+          <t>1,91; 5,01</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>405,41%</t>
+          <t>380,13%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>131,76%</t>
+          <t>152,45%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>93,79; 1226,26</t>
+          <t>85,9; 1264,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 178,15</t>
+          <t>5,13; 220,33</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30,08; 291,82</t>
+          <t>63,6; 304,62</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-2,06</t>
+          <t>-2,07</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-0,99</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,22</t>
+          <t>-1,32; 1,74</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,07; -0,41</t>
+          <t>-4,01; -0,36</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,76; -0,07</t>
+          <t>-2,17; 0,27</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-19,5%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-44,43%</t>
+          <t>-44,49%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-38,11%</t>
+          <t>-28,16%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-72,11; 65,2</t>
+          <t>-45,9; 109,82</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-66,75; -9,05</t>
+          <t>-67,56; -7,76</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-65,88; -3,72</t>
+          <t>-52,04; 11,6</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>1,01</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,43</t>
+          <t>0,7; 2,4</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,27</t>
+          <t>-0,38; 1,41</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,6</t>
+          <t>0,42; 1,69</t>
         </is>
       </c>
     </row>
@@ -1362,17 +1362,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>24,69; 159,33</t>
+          <t>33,6; 157,67</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 38,12</t>
+          <t>-9,56; 44,06</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5,41; 65,19</t>
+          <t>13,41; 69,32</t>
         </is>
       </c>
     </row>
